--- a/docker-authz-proxy-testcases-v6.xlsx
+++ b/docker-authz-proxy-testcases-v6.xlsx
@@ -5851,7 +5851,7 @@
   <si>
     <t>1. 确保 TC-PEER-007 中的容器和互通已建立，且 ping 可通
 2. 撤销互通
-   # docker-authz-proxy-ctl peer deny --uid-a 1003 --uid-b 1004
+   # docker-authz-proxy-ctl peer deny --uid-a 1001 --uid-b 1002
 3. 再次从 bob 容器 ping alice 容器 IP
    # docker exec bob-net-test ping -c 3 &lt;alice-net-test-ip&gt; || echo "UNREACHABLE"
 4. 再次从 alice 容器 ping bob 容器 IP

--- a/docker-authz-proxy-testcases-v6.xlsx
+++ b/docker-authz-proxy-testcases-v6.xlsx
@@ -5876,8 +5876,7 @@
 2. alice 启动容器 alice-app
    $ su - alice -c "docker run -d --name alice-app alpine sleep 3600"
 3. 建立容器级互通
-   # docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004 \
-       --container-a bob-web --container-b alice-app
+   # docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002 --container-a bob-web --container-b alice-app
 4. 获取 bob-web 容器 IP
    # docker inspect bob-web --format '{{range .NetworkSettings.Networks}}{{.IPAddress}}{{end}}'
 5. 从 alice-app 访问 bob-web
@@ -5903,8 +5902,7 @@
 2. alice 启动容器 alice-app
    $ su - alice -c "docker run -d --name alice-app alpine sleep 3600"
 3. 只为 bob-web 和 alice-app 建立容器级互通
-   # docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004 \
-       --container-a bob-web --container-b alice-app
+   # docker-authz-proxy-ctl peer allow --uid-a 1002 --uid-b 1001 --container-a bob-web --container-b alice-app
 4. 获取 alice-app IP
    # docker inspect alice-app --format '{{range .NetworkSettings.Networks}}{{.IPAddress}}{{end}}'
 5. 从 bob-other 尝试 ping alice-app
@@ -5990,7 +5988,7 @@
   <si>
     <t>1. 建立多条记录：用户级互通 + bob-web/alice-app 容器级互通
 2. 双重过滤
-   # docker-authz-proxy-ctl peer list --uid 1003 --container bob-web</t>
+   # docker-authz-proxy-ctl peer list --uid 1001 --container bob-web</t>
   </si>
   <si>
     <t>• 只显示同时满足 uid=1003 且包含 bob-web 容器的记录（1条容器级互通）
@@ -6007,9 +6005,9 @@
   </si>
   <si>
     <t>1. 建立用户级互通
-   # docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004
+   # docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002
 2. 再次执行相同命令
-   # docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004
+   # docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002
 3. 查看互通记录
    # docker-authz-proxy-ctl peer list</t>
   </si>
@@ -8805,7 +8803,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="10" ht="120" customHeight="1" spans="1:6">
+    <row r="10" ht="139" customHeight="1" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>863</v>
       </c>
@@ -8825,7 +8823,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="11" ht="120" customHeight="1" spans="1:6">
+    <row r="11" ht="179" customHeight="1" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>868</v>
       </c>
@@ -8845,7 +8843,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="12" ht="120" customHeight="1" spans="1:6">
+    <row r="12" ht="226" customHeight="1" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>873</v>
       </c>

--- a/docker-authz-proxy-testcases-v6.xlsx
+++ b/docker-authz-proxy-testcases-v6.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="965">
   <si>
     <t>模块</t>
   </si>
@@ -6048,7 +6048,7 @@
     <t>1. bob 启动容器 bob-web
    $ su - bob -c "docker run -d --name bob-web nginx:alpine"
 2. 尝试将 bob-web 指定为 alice 的容器建立互通
-   # docker-authz-proxy-ctl peer allow --uid-a 1004 --uid-b 1003 \
+   # docker-authz-proxy-ctl peer allow --uid-a 1002 --uid-b 1001 \
        --container-a bob-web --container-b bob-web</t>
   </si>
   <si>
@@ -6066,13 +6066,13 @@
   </si>
   <si>
     <t>1. 只指定一个用户
-   # docker-authz-proxy-ctl peer allow --uid-a 1003
+   # docker-authz-proxy-ctl peer allow --uid-a 1001
    echo "exit: $?"
 2. 不指定任何用户
    # docker-authz-proxy-ctl peer allow
    echo "exit: $?"
 3. container-a 和 container-b 只指定一个
-   # docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004 --container-a bob-web
+   # docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002 --container-a bob-web
    echo "exit: $?"</t>
   </si>
   <si>
@@ -6091,7 +6091,7 @@
   </si>
   <si>
     <t>1. 建立 bob 和 alice 用户级互通
-   # docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004
+   # docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002
 2. ywyh 启动容器
    $ su - ywyh -c "docker run -d --name ywyh-test alpine sleep 3600"
 3. bob 启动容器
@@ -6117,12 +6117,15 @@
   <si>
     <t>Linux 系统，docker-authz-proxy 服务运行中
 bob (uid=1003) 和 alice (uid=1004) 已创建，均为普通用户
-已通过 docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004 建立用户级互通
+已通过 docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002建立用户级互通
 bob 容器 bob-traffic-test 和 alice 容器 alice-traffic-test 均已启动（镜像 alpine，sleep 3600）
 已安装 iperf3、curl、netcat（nc）等工具（或使用 alpine 内置工具）</t>
   </si>
   <si>
     <t>1. 在 alice 容器启动 TCP 监听（端口 8080）
+ su - alice -c "docker run -d --name alice-traffic-test alpine sleep 3600"
+su - bob -c "docker run -d --name bob-traffic-test alpine sleep 3600"
+docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002
    # docker exec -d alice-traffic-test nc -lk -p 8080
 2. 获取 alice 容器 IP
    # ALICE_IP=$(docker inspect alice-traffic-test --format '{{range .NetworkSettings.Networks}}{{.IPAddress}} {{end}}' | awk '{print $NF}')
@@ -6142,6 +6145,13 @@
   </si>
   <si>
     <t>验证互通容器间 UDP 报文可正常传输</t>
+  </si>
+  <si>
+    <t>Linux 系统，docker-authz-proxy 服务运行中
+bob (uid=1003) 和 alice (uid=1004) 已创建，均为普通用户
+已通过 docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004 建立用户级互通
+bob 容器 bob-traffic-test 和 alice 容器 alice-traffic-test 均已启动（镜像 alpine，sleep 3600）
+已安装 iperf3、curl、netcat（nc）等工具（或使用 alpine 内置工具）</t>
   </si>
   <si>
     <t>1. 在 alice 容器启动 UDP 监听（端口 9090）
@@ -6169,7 +6179,7 @@
     <t>1. alice 启动 nginx 容器（提供 HTTP 服务）
    $ su - alice -c "docker run -d --name alice-nginx nginx:alpine"
 2. 建立用户级互通（若未建立）
-   # docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004
+   # docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002
 3. 获取 alice-nginx 容器 IP
    # NGINX_IP=$(docker inspect alice-nginx --format '{{range .NetworkSettings.Networks}}{{.IPAddress}} {{end}}' | awk '{print $NF}')
 4. bob 启动容器并访问 alice-nginx
@@ -8618,7 +8628,8 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="4" width="35" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="38.1681415929204" customWidth="1"/>
     <col min="5" max="5" width="65" customWidth="1"/>
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
@@ -9003,7 +9014,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="20" ht="120" customHeight="1" spans="1:6">
+    <row r="20" ht="150" customHeight="1" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>913</v>
       </c>
@@ -9023,7 +9034,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="21" ht="120" customHeight="1" spans="1:6">
+    <row r="21" ht="198" customHeight="1" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>918</v>
       </c>
@@ -9043,7 +9054,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="22" ht="120" customHeight="1" spans="1:6">
+    <row r="22" ht="195" customHeight="1" spans="1:6">
       <c r="A22" s="2" t="s">
         <v>923</v>
       </c>
@@ -9063,7 +9074,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="23" ht="120" customHeight="1" spans="1:6">
+    <row r="23" ht="177" customHeight="1" spans="1:6">
       <c r="A23" s="2" t="s">
         <v>929</v>
       </c>
@@ -9074,133 +9085,133 @@
         <v>931</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="24" ht="165" customHeight="1" spans="1:6">
+      <c r="A24" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="24" ht="120" customHeight="1" spans="1:6">
-      <c r="A24" s="2" t="s">
-        <v>934</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>926</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="25" ht="120" customHeight="1" spans="1:6">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="25" ht="165" customHeight="1" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="26" ht="120" customHeight="1" spans="1:6">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="26" ht="162" customHeight="1" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="27" ht="120" customHeight="1" spans="1:6">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="27" ht="194" customHeight="1" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="28" ht="120" customHeight="1" spans="1:6">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="28" ht="235" customHeight="1" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="29" ht="120" customHeight="1" spans="1:6">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="29" ht="235" customHeight="1" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
   </sheetData>

--- a/docker-authz-proxy-testcases-v6.xlsx
+++ b/docker-authz-proxy-testcases-v6.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" firstSheet="1" activeTab="12"/>
+    <workbookView windowHeight="17655" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例汇总" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="1014">
   <si>
     <t>模块</t>
   </si>
@@ -1252,6 +1252,309 @@
 • 对比：bob 尝试操作 alice 容器会返回 403</t>
   </si>
   <si>
+    <t>TC-ROOT-022</t>
+  </si>
+  <si>
+    <t>root 用镜像名将自己的镜像设为 public</t>
+  </si>
+  <si>
+    <t>验证 root 可以通过镜像名（含 tag）将镜像标记为 public，其他用户随后可拉取该镜像</t>
+  </si>
+  <si>
+    <t>系统环境：
+- docker-authz-proxy 服务正在运行
+- /var/lib/docker-authz/owners.db 数据库可访问
+- docker-authz-proxy-ctl 已安装并在 PATH 中
+- Docker daemon 通过代理 socket /var/run/docker-authz.sock 提供服务
+- 测试用户 alice (uid=1001)、bob (uid=1002) 已创建
+- root 用户已登录
+具体前提：
+- root 已拉取镜像 alpine:3.18（已记录在 DB 中）</t>
+  </si>
+  <si>
+    <t>1. 以 root 身份执行：
+   docker-authz-proxy-ctl image set-public alpine:3.18
+2. 验证命令输出包含 'marked as public'
+3. 查看镜像列表确认状态：
+   docker-authz-proxy-ctl image list
+4. 以 alice 身份尝试拉取该镜像：
+   sudo -u alice docker -H unix:///run/docker-authz/alice/docker.sock pull alpine:3.18
+5. 确认 alice 拉取成功</t>
+  </si>
+  <si>
+    <t>1. 命令输出：image alpine:3.18 (&lt;short_id&gt;) marked as public
+2. image list 中该镜像 public 列显示 true
+3. alice 拉取成功，无权限错误
+4. DB 中 is_public=1</t>
+  </si>
+  <si>
+    <t>TC-ROOT-023</t>
+  </si>
+  <si>
+    <t>root 用短 ID 将其他用户的镜像设为 public</t>
+  </si>
+  <si>
+    <t>验证 root 可以通过镜像短 ID 将其他用户（alice）拥有的镜像标记为 public</t>
+  </si>
+  <si>
+    <t>系统环境：
+- docker-authz-proxy 服务正在运行
+- /var/lib/docker-authz/owners.db 数据库可访问
+- docker-authz-proxy-ctl 已安装并在 PATH 中
+- Docker daemon 通过代理 socket /var/run/docker-authz.sock 提供服务
+- 测试用户 alice (uid=1001)、bob (uid=1002) 已创建
+- root 用户已登录
+具体前提：
+- alice 已拉取镜像 nginx:latest，DB 中记录其 image_id（如 a1b2c3d4e5f6...）
+- root 通过 image list 获取该镜像的短 ID（前12位）</t>
+  </si>
+  <si>
+    <t>1. root 查看镜像列表获取 alice 镜像的短 ID：
+   docker-authz-proxy-ctl image list
+   # 记录 nginx 镜像的 image_id 前12位，如 a1b2c3d4e5f6
+2. root 用短 ID 设置为 public：
+   docker-authz-proxy-ctl image set-public a1b2c3d4e5f6
+3. 验证命令输出包含 'marked as public'
+4. 再次执行 image list，确认该镜像 public=true
+5. 以 bob 身份拉取该镜像：
+   sudo -u bob docker -H unix:///var/run/docker-authz.sock pull nginx:latest</t>
+  </si>
+  <si>
+    <t>1. image list 显示 alice 的 nginx 镜像
+2. 命令输出：image a1b2c3d4e5f6 (&lt;short_id&gt;) marked as public
+3. image list 中该镜像 public 列变为 true
+4. bob 拉取成功，无权限错误</t>
+  </si>
+  <si>
+    <t>TC-ROOT-024</t>
+  </si>
+  <si>
+    <t>root 用镜像名将 public 镜像设回 private</t>
+  </si>
+  <si>
+    <t>验证 root 可以通过镜像名将已标记为 public 的镜像重新设为 private，其他用户随后无法拉取</t>
+  </si>
+  <si>
+    <t>系统环境：
+- docker-authz-proxy 服务正在运行
+- /var/lib/docker-authz/owners.db 数据库可访问
+- docker-authz-proxy-ctl 已安装并在 PATH 中
+- Docker daemon 通过代理 socket /var/run/docker-authz.sock 提供服务
+- 测试用户 alice (uid=1001)、bob (uid=1002) 已创建
+- root 用户已登录
+具体前提：
+- alpine:3.18 已被标记为 public（TC-ROOT-022 执行后的状态）</t>
+  </si>
+  <si>
+    <t>1. root 将镜像设回 private：
+   docker-authz-proxy-ctl image set-public --public=false alpine:3.18
+2. 验证命令输出包含 'marked as private'
+3. 查看镜像列表确认状态：
+   docker-authz-proxy-ctl image list
+4. 以 alice 身份尝试拉取该镜像（alice 不是 owner）：
+   sudo -u alice docker -H unix:///var/run/docker-authz.sock pull alpine:3.18
+5. 确认 alice 拉取被拒绝</t>
+  </si>
+  <si>
+    <t>1. 命令输出：image alpine:3.18 (&lt;short_id&gt;) marked as private
+2. image list 中该镜像 public 列显示 false
+3. alice 拉取失败，返回权限错误（403 或 unauthorized）
+4. DB 中 is_public=0</t>
+  </si>
+  <si>
+    <t>TC-ROOT-025</t>
+  </si>
+  <si>
+    <t>root 用短 ID 将 public 镜像设回 private</t>
+  </si>
+  <si>
+    <t>验证 root 可以通过镜像短 ID 将 public 镜像重新设为 private</t>
+  </si>
+  <si>
+    <t>系统环境：
+- docker-authz-proxy 服务正在运行
+- /var/lib/docker-authz/owners.db 数据库可访问
+- docker-authz-proxy-ctl 已安装并在 PATH 中
+- Docker daemon 通过代理 socket /var/run/docker-authz.sock 提供服务
+- 测试用户 alice (uid=1001)、bob (uid=1002) 已创建
+- root 用户已登录
+具体前提：
+- nginx:latest（alice 所有）已被标记为 public（TC-ROOT-023 执行后的状态）
+- 已知该镜像短 ID（如 a1b2c3d4e5f6）</t>
+  </si>
+  <si>
+    <t>1. root 用短 ID 设置为 private：
+   docker-authz-proxy-ctl image set-public --public=false a1b2c3d4e5f6
+2. 验证命令输出包含 'marked as private'
+3. 查看镜像列表确认状态：
+   docker-authz-proxy-ctl image list
+4. 以 bob 身份尝试拉取该镜像：
+   sudo -u bob docker -H unix:///var/run/docker-authz.sock pull nginx:latest
+5. 确认 bob 拉取被拒绝</t>
+  </si>
+  <si>
+    <t>1. 命令输出：image a1b2c3d4e5f6 (&lt;short_id&gt;) marked as private
+2. image list 中该镜像 public 列变为 false
+3. bob 拉取失败，返回权限错误
+4. DB 中 is_public=0</t>
+  </si>
+  <si>
+    <t>TC-ROOT-026</t>
+  </si>
+  <si>
+    <t>root image list 查看所有镜像公开状态</t>
+  </si>
+  <si>
+    <t>验证 image list 命令能正确列出所有已记录镜像及其 owner、uid、public 状态</t>
+  </si>
+  <si>
+    <t>系统环境：
+- docker-authz-proxy 服务正在运行
+- /var/lib/docker-authz/owners.db 数据库可访问
+- docker-authz-proxy-ctl 已安装并在 PATH 中
+- Docker daemon 通过代理 socket /var/run/docker-authz.sock 提供服务
+- 测试用户 alice (uid=1001)、bob (uid=1002) 已创建
+- root 用户已登录
+具体前提：
+- DB 中已有多个镜像记录（属于不同用户，public 状态各异）</t>
+  </si>
+  <si>
+    <t>1. root 执行：
+   docker-authz-proxy-ctl image list
+2. 观察输出表格的列标题和数据行
+3. 确认包含 root 自己的镜像
+4. 确认包含 alice 的镜像
+5. 确认包含 bob 的镜像
+6. 对比 DB 直接查询结果：
+   sqlite3 /var/lib/docker-authz/owners.db \
+     'SELECT image_id, owner_username, owner_uid, is_public FROM images ORDER BY owner_uid, image_id'</t>
+  </si>
+  <si>
+    <t>1. 输出包含表头：image_id / owner / uid / public
+2. 每行显示镜像短 ID（前12位）、owner 用户名、uid、public 状态（true/false）
+3. 所有用户的镜像均可见（root 视角无过滤）
+4. 与 DB 直接查询结果一致
+5. 若 DB 为空，输出 'no images recorded'</t>
+  </si>
+  <si>
+    <t>TC-ROOT-027</t>
+  </si>
+  <si>
+    <t>非 root 用户无法执行 image set-public</t>
+  </si>
+  <si>
+    <t>验证 image set-public 命令仅限 root 执行，普通用户执行时因无法访问 DB 而失败</t>
+  </si>
+  <si>
+    <t>系统环境：
+- docker-authz-proxy 服务正在运行
+- /var/lib/docker-authz/owners.db 数据库可访问
+- docker-authz-proxy-ctl 已安装并在 PATH 中
+- Docker daemon 通过代理 socket /var/run/docker-authz.sock 提供服务
+- 测试用户 alice (uid=1001)、bob (uid=1002) 已创建
+- root 用户已登录
+具体前提：
+- /var/lib/docker-authz/owners.db 文件权限为 root:root 600 或 640
+- alice 无法直接读写该 DB 文件</t>
+  </si>
+  <si>
+    <t>1. 以 alice 身份执行：
+   sudo -u alice docker-authz-proxy-ctl image set-public alpine:3.18
+2. 观察错误输出
+3. 以 bob 身份执行：
+   sudo -u bob docker-authz-proxy-ctl image set-public --public=false nginx:latest
+4. 观察错误输出
+5. 确认 DB 中镜像状态未发生变化</t>
+  </si>
+  <si>
+    <t>1. alice 执行失败，输出类似：error: open db: unable to open database file: permission denied
+2. bob 执行失败，同样权限错误
+3. DB 中镜像 is_public 值未被修改
+4. 命令退出码非 0</t>
+  </si>
+  <si>
+    <t>TC-ROOT-028</t>
+  </si>
+  <si>
+    <t>对不存在的镜像执行 set-public 报错</t>
+  </si>
+  <si>
+    <t>验证当指定的镜像名或 ID 在 DB 中不存在时，命令返回明确错误信息</t>
+  </si>
+  <si>
+    <t>系统环境：
+- docker-authz-proxy 服务正在运行
+- /var/lib/docker-authz/owners.db 数据库可访问
+- docker-authz-proxy-ctl 已安装并在 PATH 中
+- Docker daemon 通过代理 socket /var/run/docker-authz.sock 提供服务
+- 测试用户 alice (uid=1001)、bob (uid=1002) 已创建
+- root 用户已登录
+具体前提：
+- DB 中不存在名为 nonexistent:latest 的镜像记录
+- DB 中不存在以 deadbeef1234 开头的镜像 ID</t>
+  </si>
+  <si>
+    <t>1. root 用不存在的镜像名执行：
+   docker-authz-proxy-ctl image set-public nonexistent:latest
+2. 观察错误输出
+3. root 用不存在的短 ID 执行：
+   docker-authz-proxy-ctl image set-public deadbeef1234
+4. 观察错误输出
+5. 确认命令退出码非 0</t>
+  </si>
+  <si>
+    <t>1. 步骤1 输出：error: 镜像 "nonexistent:latest" 在归属 DB 中不存在
+2. 步骤3 输出：error: 镜像 "deadbeef1234" 在归属 DB 中不存在
+3. 命令退出码为 1
+4. DB 内容无任何变化</t>
+  </si>
+  <si>
+    <t>TC-ROOT-029</t>
+  </si>
+  <si>
+    <t>public 镜像对所有用户可见验证（端到端）</t>
+  </si>
+  <si>
+    <t>端到端验证：root 将镜像设为 public 后，系统中所有普通用户均可通过代理拉取该镜像，且 owner 不变</t>
+  </si>
+  <si>
+    <t>系统环境：
+- docker-authz-proxy 服务正在运行
+- /var/lib/docker-authz/owners.db 数据库可访问
+- docker-authz-proxy-ctl 已安装并在 PATH 中
+- Docker daemon 通过代理 socket /var/run/docker-authz.sock 提供服务
+- 测试用户 alice (uid=1001)、bob (uid=1002) 已创建
+- root 用户已登录
+具体前提：
+- root 已拉取 busybox:latest 并记录在 DB 中（is_public=0）
+- alice 和 bob 均未拉取过该镜像</t>
+  </si>
+  <si>
+    <t>1. 确认初始状态（alice 无法拉取）：
+   sudo -u alice docker -H unix:///var/run/docker-authz.sock pull busybox:latest
+   # 预期失败
+2. root 将 busybox:latest 设为 public：
+   docker-authz-proxy-ctl image set-public busybox:latest
+3. alice 拉取 public 镜像：
+   sudo -u alice docker -H unix:///var/run/docker-authz.sock pull busybox:latest
+4. bob 拉取 public 镜像：
+   sudo -u bob docker -H unix:///var/run/docker-authz.sock pull busybox:latest
+5. 确认 DB 中 owner 仍为 root：
+   docker-authz-proxy-ctl image list
+6. root 将镜像设回 private：
+   docker-authz-proxy-ctl image set-public --public=false busybox:latest
+7. 再次以 alice 身份拉取，确认被拒绝</t>
+  </si>
+  <si>
+    <t>1. 步骤1：alice 拉取失败（权限错误）
+2. 步骤2：命令输出 marked as public
+3. 步骤3：alice 拉取成功
+4. 步骤4：bob 拉取成功
+5. 步骤5：image list 中 busybox owner 仍为 root，public=true
+6. 步骤6：命令输出 marked as private
+7. 步骤7：alice 拉取再次失败，权限错误</t>
+  </si>
+  <si>
     <t>TC-SUDO-001</t>
   </si>
   <si>
@@ -6181,7 +6484,8 @@
 2. 建立用户级互通（若未建立）
    # docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002
 3. 获取 alice-nginx 容器 IP
-   # NGINX_IP=$(docker inspect alice-nginx --format '{{range .NetworkSettings.Networks}}{{.IPAddress}} {{end}}' | awk '{print $NF}')
+   # NGINX_IP=$(docker inspect alice-nginx \
+    --format '{{range $name, $cfg := .NetworkSettings.Networks}}{{if eq (slice $name 0 4) "peer"}}{{$cfg.IPAddress}}{{end}}{{end}}')
 4. bob 启动容器并访问 alice-nginx
    $ su - bob -c "docker run --rm alpine wget -qO- http://$NGINX_IP | head -3"</t>
   </si>
@@ -6199,17 +6503,21 @@
     <t>验证互通容器间可稳定传输大块数据，无丢包或截断</t>
   </si>
   <si>
-    <t>1. 在 alice 容器启动接收端（端口 7070，写入 /dev/null）
-   # docker exec -d alice-traffic-test sh -c "nc -lk -p 7070 &gt; /dev/null"
+    <t xml:space="preserve">1. 在 alice 容器启动接收端（端口 7070，写入 /dev/null）
+ docker exec alice-traffic-test sh -c "pkill nc 2&gt;/dev/null; while true; do nc -l -p 7070 &gt;/dev/null; done &amp;"
 2. 获取 alice 容器 IP
-   # ALICE_IP=$(docker inspect alice-traffic-test --format '{{range .NetworkSettings.Networks}}{{.IPAddress}} {{end}}' | awk '{print $NF}')
+   # ALICE_IP=$(docker inspect alice-traffic-test \
+    --format '{{(index .NetworkSettings.Networks "peer-1001-1002").IPAddress}}')
 3. 从 bob 容器发送 100MB 数据并计时
-   # docker exec bob-traffic-test sh -c \
-     "dd if=/dev/zero bs=1M count=100 2&gt;/dev/null | nc -w5 $ALICE_IP 7070"
-   # echo "exit: $?"</t>
-  </si>
-  <si>
-    <t>• dd + nc 命令正常退出，exit code = 0
+   #docker exec bob-traffic-test sh -c "
+    dd if=/dev/zero of=/tmp/payload bs=1M count=100 &amp;&amp;
+    time nc -w10 $ALICE_IP 7070 &lt;/tmp/payload
+    rm /tmp/payload
+  "
+  </t>
+  </si>
+  <si>
+    <t>• dd + nc 命令正常退出
 • 100MB 数据传输完成，无报错
 • 传输速率合理（容器内网络，通常 &gt; 100 MB/s）</t>
   </si>
@@ -6224,12 +6532,13 @@
   </si>
   <si>
     <t>1. 在 alice 容器安装并启动 iperf3 服务端
-   # docker exec alice-traffic-test sh -c "apk add -q iperf3 &amp;&amp; iperf3 -s -D"
+   # docker exec alice-traffic-test sh -c "apk add -q iperf &amp;&amp; iperf -s -D"
 2. 获取 alice 容器 IP
-   # ALICE_IP=$(docker inspect alice-traffic-test --format '{{range .NetworkSettings.Networks}}{{.IPAddress}} {{end}}' | awk '{print $NF}')
+   # ALICE_IP=$(docker inspect alice-traffic-test \
+    --format '{{(index .NetworkSettings.Networks "peer-1001-1002").IPAddress}}')
 3. 在 bob 容器安装 iperf3 并运行客户端（测试 10 秒）
    # docker exec bob-traffic-test sh -c \
-     "apk add -q iperf3 &amp;&amp; iperf3 -c $ALICE_IP -t 10 -P 4"</t>
+     "apk add -q iperf3 &amp;&amp; iperf -c $ALICE_IP -t 10 -P 4"</t>
   </si>
   <si>
     <t>• iperf3 测试正常完成，输出 sender/receiver 带宽数据
@@ -6247,20 +6556,25 @@
   </si>
   <si>
     <t>1. 在 alice 容器启动多端口监听（6001~6010）
-   # for p in $(seq 6001 6010); do
-       docker exec -d alice-traffic-test nc -lk -p $p
-     done
+   # docker exec alice-traffic-test sh -c "pkill socat 2&gt;/dev/null; socat TCP-LISTEN:7070,fork,reuseaddr /dev/null &amp;"
 2. 获取 alice 容器 IP
-   # ALICE_IP=$(docker inspect alice-traffic-test --format '{{range .NetworkSettings.Networks}}{{.IPAddress}} {{end}}' | awk '{print $NF}')
+   # ALICE_IP=$(docker inspect alice-traffic-test \
+    --format '{{(index .NetworkSettings.Networks "peer-1001-1002").IPAddress}}')
 3. 从 bob 容器并发连接所有端口
-   # for p in $(seq 6001 6010); do
-       docker exec bob-traffic-test nc -zv $ALICE_IP $p &amp;
-     done
-   # wait
-   # echo "all done"</t>
-  </si>
-  <si>
-    <t>• 10 个并发连接全部成功，每个端口均输出 "open" 或 "succeeded"
+  docker exec bob-traffic-test sh -c "
+    dd if=/dev/zero of=/tmp/payload bs=1M count=100
+    time sh -c 'i=1; while [ \$i -le 10 ]; do socat -u FILE:/tmp/payload TCP:$ALICE_IP:7070; i=\$((i+1)); done'
+    rm /tmp/payload
+  "</t>
+  </si>
+  <si>
+    <t>• 10 个并发连接全部成功，每个端口均输出类似
+100+0 records in
+100+0 records out
+104857600 bytes (100.0MB) copied, 0.051432 seconds, 1.9GB/s
+real    0m 0.88s
+user    0m 0.11s
+sys     0m 0.74s
 • 无连接超时或拒绝，exit code 均为 0</t>
   </si>
   <si>
@@ -6274,13 +6588,14 @@
   </si>
   <si>
     <t>1. 建立用户级互通并确认连通
-   # docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004
-   # ALICE_IP=$(docker inspect alice-traffic-test --format '{{range .NetworkSettings.Networks}}{{.IPAddress}} {{end}}' | awk '{print $NF}')
+   # docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002
+   # ALICE_IP=$(docker inspect alice-traffic-test \
+    --format '{{(index .NetworkSettings.Networks "peer-1001-1002").IPAddress}}')
    # docker exec bob-traffic-test ping -c 2 $ALICE_IP
 2. 在 bob 容器后台持续 ping alice 容器
    # docker exec -d bob-traffic-test sh -c "ping $ALICE_IP &gt; /tmp/ping.log 2&gt;&amp;1"
 3. 撤销互通
-   # docker-authz-proxy-ctl peer deny --uid-a 1003 --uid-b 1004
+   # docker-authz-proxy-ctl peer deny --uid-a 1001 --uid-b 1002
 4. 等待 2 秒后检查 ping 日志
    # sleep 2
    # docker exec bob-traffic-test cat /tmp/ping.log | tail -5
@@ -6300,6 +6615,13 @@
   </si>
   <si>
     <t>验证容器级互通下，只有指定容器间有流量，同用户其他容器无法通信</t>
+  </si>
+  <si>
+    <t>Linux 系统，docker-authz-proxy 服务运行中
+bob (uid=1003) 和 alice (uid=1004) 已创建，均为普通用户
+已通过 docker-authz-proxy-ctl peer allow --uid-a 1001 --uid-b 1002 建立用户级互通
+bob 容器 bob-traffic-test 和 alice 容器 alice-traffic-test 均已启动（镜像 alpine，sleep 3600）
+已安装 iperf3、curl、netcat（nc）等工具（或使用 alpine 内置工具）</t>
   </si>
   <si>
     <t>1. bob 启动两个容器：bob-allowed（参与互通）和 bob-blocked（不参与）
@@ -6308,10 +6630,9 @@
 2. alice 启动容器 alice-server，运行 HTTP 服务
    $ su - alice -c "docker run -d --name alice-server nginx:alpine"
 3. 建立容器级互通（只允许 bob-allowed &lt;-&gt; alice-server）
-   # docker-authz-proxy-ctl peer allow --uid-a 1003 --uid-b 1004 \
-       --container-a bob-allowed --container-b alice-server
+   # docker-authz-proxy-ctl peer allow --uid-a 1002 --uid-b 1001 --container-a bob-allowed --container-b alice-server
 4. 获取 alice-server IP
-   # SERVER_IP=$(docker inspect alice-server --format '{{range .NetworkSettings.Networks}}{{.IPAddress}} {{end}}' | awk '{print $NF}')
+   # SERVER_IP=$(docker inspect alice-server --format '{{(index .NetworkSettings.Networks  "peer-1001-1002").IPAddress}}'）
 5. bob-allowed 访问 alice-server（应成功）
    # docker exec bob-allowed wget -qO- http://$SERVER_IP | head -1
 6. bob-blocked 访问 alice-server（应失败）
@@ -6333,7 +6654,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6357,6 +6678,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -6951,16 +7278,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
@@ -6969,119 +7293,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="7">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="8">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="41" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="42" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="44" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="45" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="44" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="46" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="45" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="46" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7125,6 +7452,9 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -7146,7 +7476,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -7503,156 +7833,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="19">
         <v>8</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="21">
         <v>21</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <v>15</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="21">
         <v>10</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <v>13</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="21">
         <v>12</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <v>13</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="18" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="21">
         <v>10</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <v>18</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="21">
         <v>14</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <v>10</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" ht="13.9" customHeight="1" spans="1:3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="22">
         <v>28</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="22" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="23">
         <v>152</v>
       </c>
-      <c r="C14" s="23"/>
+      <c r="C14" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7696,362 +8026,362 @@
     </row>
     <row r="2" ht="130" customHeight="1" spans="1:6">
       <c r="A2" s="6" t="s">
-        <v>595</v>
+        <v>643</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>596</v>
+        <v>644</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>597</v>
+        <v>645</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>599</v>
+        <v>647</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>600</v>
+        <v>648</v>
       </c>
     </row>
     <row r="3" ht="130" customHeight="1" spans="1:6">
       <c r="A3" s="6" t="s">
-        <v>601</v>
+        <v>649</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>602</v>
+        <v>650</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>603</v>
+        <v>651</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>604</v>
+        <v>652</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>605</v>
+        <v>653</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>606</v>
+        <v>654</v>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1" spans="1:6">
       <c r="A4" s="6" t="s">
-        <v>607</v>
+        <v>655</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>608</v>
+        <v>656</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>610</v>
+        <v>658</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>611</v>
+        <v>659</v>
       </c>
     </row>
     <row r="5" ht="130" customHeight="1" spans="1:6">
       <c r="A5" s="6" t="s">
-        <v>612</v>
+        <v>660</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>613</v>
+        <v>661</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>614</v>
+        <v>662</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>616</v>
+        <v>664</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>617</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6" ht="130" customHeight="1" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>618</v>
+        <v>666</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>619</v>
+        <v>667</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>620</v>
+        <v>668</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>621</v>
+        <v>669</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>622</v>
+        <v>670</v>
       </c>
     </row>
     <row r="7" ht="130" customHeight="1" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>623</v>
+        <v>671</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>624</v>
+        <v>672</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>625</v>
+        <v>673</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>626</v>
+        <v>674</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>627</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8" ht="130" customHeight="1" spans="1:6">
       <c r="A8" s="6" t="s">
-        <v>628</v>
+        <v>676</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>629</v>
+        <v>677</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>630</v>
+        <v>678</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>631</v>
+        <v>679</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>632</v>
+        <v>680</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>633</v>
+        <v>681</v>
       </c>
     </row>
     <row r="9" ht="130" customHeight="1" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>634</v>
+        <v>682</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>635</v>
+        <v>683</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>636</v>
+        <v>684</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>637</v>
+        <v>685</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>638</v>
+        <v>686</v>
       </c>
     </row>
     <row r="10" ht="130" customHeight="1" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>639</v>
+        <v>687</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>640</v>
+        <v>688</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>641</v>
+        <v>689</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>642</v>
+        <v>690</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>643</v>
+        <v>691</v>
       </c>
     </row>
     <row r="11" ht="130" customHeight="1" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>644</v>
+        <v>692</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>645</v>
+        <v>693</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>646</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>598</v>
-      </c>
       <c r="E11" s="6" t="s">
-        <v>647</v>
+        <v>695</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>648</v>
+        <v>696</v>
       </c>
     </row>
     <row r="12" ht="130" customHeight="1" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>649</v>
+        <v>697</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>650</v>
+        <v>698</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>651</v>
+        <v>699</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>652</v>
+        <v>700</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>653</v>
+        <v>701</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>654</v>
+        <v>702</v>
       </c>
     </row>
     <row r="13" ht="130" customHeight="1" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>655</v>
+        <v>703</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>656</v>
+        <v>704</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>657</v>
+        <v>705</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>658</v>
+        <v>706</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>659</v>
+        <v>707</v>
       </c>
     </row>
     <row r="14" ht="130" customHeight="1" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>660</v>
+        <v>708</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>661</v>
+        <v>709</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>662</v>
+        <v>710</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>663</v>
+        <v>711</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>664</v>
+        <v>712</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
     </row>
     <row r="15" ht="130" customHeight="1" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>666</v>
+        <v>714</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>667</v>
+        <v>715</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>668</v>
+        <v>716</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>669</v>
+        <v>717</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>670</v>
+        <v>718</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>671</v>
+        <v>719</v>
       </c>
     </row>
     <row r="16" ht="130" customHeight="1" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>672</v>
+        <v>720</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>673</v>
+        <v>721</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>674</v>
+        <v>722</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>675</v>
+        <v>723</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>676</v>
+        <v>724</v>
       </c>
     </row>
     <row r="17" ht="130" customHeight="1" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>677</v>
+        <v>725</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>678</v>
+        <v>726</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>679</v>
+        <v>727</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>680</v>
+        <v>728</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>681</v>
+        <v>729</v>
       </c>
     </row>
     <row r="18" ht="130" customHeight="1" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>682</v>
+        <v>730</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>683</v>
+        <v>731</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>684</v>
+        <v>732</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>685</v>
+        <v>733</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>686</v>
+        <v>734</v>
       </c>
     </row>
     <row r="19" ht="130" customHeight="1" spans="1:6">
       <c r="A19" s="6" t="s">
-        <v>687</v>
+        <v>735</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>688</v>
+        <v>736</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>689</v>
+        <v>737</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>598</v>
+        <v>646</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>690</v>
+        <v>738</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>691</v>
+        <v>739</v>
       </c>
     </row>
   </sheetData>
@@ -8096,282 +8426,282 @@
     </row>
     <row r="2" ht="130" customHeight="1" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>692</v>
+        <v>740</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>693</v>
+        <v>741</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>694</v>
+        <v>742</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>695</v>
+        <v>743</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>696</v>
+        <v>744</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>697</v>
+        <v>745</v>
       </c>
     </row>
     <row r="3" ht="130" customHeight="1" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>698</v>
+        <v>746</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>699</v>
+        <v>747</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>700</v>
+        <v>748</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>702</v>
+        <v>750</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>703</v>
+        <v>751</v>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>704</v>
+        <v>752</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>705</v>
+        <v>753</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>706</v>
+        <v>754</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>707</v>
+        <v>755</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>708</v>
+        <v>756</v>
       </c>
     </row>
     <row r="5" ht="130" customHeight="1" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>709</v>
+        <v>757</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>710</v>
+        <v>758</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>711</v>
+        <v>759</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>712</v>
+        <v>760</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>713</v>
+        <v>761</v>
       </c>
     </row>
     <row r="6" ht="130" customHeight="1" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>714</v>
+        <v>762</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>715</v>
+        <v>763</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>716</v>
+        <v>764</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>717</v>
+        <v>765</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>718</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7" ht="130" customHeight="1" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>719</v>
+        <v>767</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>720</v>
+        <v>768</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>721</v>
+        <v>769</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>722</v>
+        <v>770</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>723</v>
+        <v>771</v>
       </c>
     </row>
     <row r="8" ht="130" customHeight="1" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>724</v>
+        <v>772</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>725</v>
+        <v>773</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>726</v>
+        <v>774</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>727</v>
+        <v>775</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>728</v>
+        <v>776</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>729</v>
+        <v>777</v>
       </c>
     </row>
     <row r="9" ht="130" customHeight="1" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>730</v>
+        <v>778</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>731</v>
+        <v>779</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>732</v>
+        <v>780</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>733</v>
+        <v>781</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>734</v>
+        <v>782</v>
       </c>
     </row>
     <row r="10" ht="130" customHeight="1" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>735</v>
+        <v>783</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>736</v>
+        <v>784</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>737</v>
+        <v>785</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>738</v>
+        <v>786</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>739</v>
+        <v>787</v>
       </c>
     </row>
     <row r="11" ht="130" customHeight="1" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>740</v>
+        <v>788</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>741</v>
+        <v>789</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>742</v>
+        <v>790</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>743</v>
+        <v>791</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>744</v>
+        <v>792</v>
       </c>
     </row>
     <row r="12" ht="130" customHeight="1" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>745</v>
+        <v>793</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>746</v>
+        <v>794</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>747</v>
+        <v>795</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>748</v>
+        <v>796</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>749</v>
+        <v>797</v>
       </c>
     </row>
     <row r="13" ht="130" customHeight="1" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>750</v>
+        <v>798</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>751</v>
+        <v>799</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>752</v>
+        <v>800</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>753</v>
+        <v>801</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>754</v>
+        <v>802</v>
       </c>
     </row>
     <row r="14" ht="130" customHeight="1" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>755</v>
+        <v>803</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>756</v>
+        <v>804</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>757</v>
+        <v>805</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>758</v>
+        <v>806</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>759</v>
+        <v>807</v>
       </c>
     </row>
     <row r="15" ht="130" customHeight="1" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>760</v>
+        <v>808</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>761</v>
+        <v>809</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>762</v>
+        <v>810</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>763</v>
+        <v>811</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>764</v>
+        <v>812</v>
       </c>
     </row>
   </sheetData>
@@ -8414,204 +8744,204 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="130" customHeight="1" spans="1:6">
+    <row r="2" ht="312" customHeight="1" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>765</v>
+        <v>813</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>766</v>
+        <v>814</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>767</v>
+        <v>815</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>768</v>
+        <v>816</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>769</v>
+        <v>817</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="3" ht="130" customHeight="1" spans="1:6">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="3" ht="189" customHeight="1" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>771</v>
+        <v>819</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>772</v>
+        <v>820</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>773</v>
+        <v>821</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>774</v>
+        <v>822</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>775</v>
+        <v>823</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>776</v>
+        <v>824</v>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>777</v>
+        <v>825</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>778</v>
+        <v>826</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>779</v>
+        <v>827</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>780</v>
+        <v>828</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>781</v>
+        <v>829</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>782</v>
+        <v>830</v>
       </c>
     </row>
     <row r="5" ht="130" customHeight="1" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>783</v>
+        <v>831</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>784</v>
+        <v>832</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>785</v>
+        <v>833</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>780</v>
+        <v>828</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>786</v>
+        <v>834</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="6" ht="130" customHeight="1" spans="1:6">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="6" ht="256" customHeight="1" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>789</v>
+        <v>837</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>790</v>
+        <v>838</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>780</v>
+        <v>828</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>791</v>
+        <v>839</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="7" ht="130" customHeight="1" spans="1:6">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="7" ht="216" customHeight="1" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>793</v>
+        <v>841</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>794</v>
+        <v>842</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>795</v>
+        <v>843</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>780</v>
+        <v>828</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>796</v>
+        <v>844</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="8" ht="130" customHeight="1" spans="1:6">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="8" ht="219" customHeight="1" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>798</v>
+        <v>846</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>799</v>
+        <v>847</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>800</v>
+        <v>848</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>801</v>
+        <v>849</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>802</v>
+        <v>850</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="9" ht="130" customHeight="1" spans="1:6">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="9" ht="228" customHeight="1" spans="1:6">
       <c r="A9" s="4" t="s">
-        <v>804</v>
+        <v>852</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>805</v>
+        <v>853</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>806</v>
+        <v>854</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>807</v>
+        <v>855</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>808</v>
+        <v>856</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="10" ht="130" customHeight="1" spans="1:6">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="10" ht="229" customHeight="1" spans="1:6">
       <c r="A10" s="4" t="s">
-        <v>810</v>
+        <v>858</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>811</v>
+        <v>859</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>812</v>
+        <v>860</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>813</v>
+        <v>861</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>814</v>
+        <v>862</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="11" ht="130" customHeight="1" spans="1:6">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="11" ht="261" customHeight="1" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>816</v>
+        <v>864</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>817</v>
+        <v>865</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>818</v>
+        <v>866</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>819</v>
+        <v>867</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>820</v>
+        <v>868</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>821</v>
+        <v>869</v>
       </c>
     </row>
   </sheetData>
@@ -8656,562 +8986,562 @@
     </row>
     <row r="2" ht="120" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>822</v>
+        <v>870</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>823</v>
+        <v>871</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>824</v>
+        <v>872</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>826</v>
+        <v>874</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>827</v>
+        <v>875</v>
       </c>
     </row>
     <row r="3" ht="120" customHeight="1" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>828</v>
+        <v>876</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>829</v>
+        <v>877</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>830</v>
+        <v>878</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>831</v>
+        <v>879</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>832</v>
+        <v>880</v>
       </c>
     </row>
     <row r="4" ht="144" customHeight="1" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>833</v>
+        <v>881</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>834</v>
+        <v>882</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>835</v>
+        <v>883</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>836</v>
+        <v>884</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>837</v>
+        <v>885</v>
       </c>
     </row>
     <row r="5" ht="120" customHeight="1" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>838</v>
+        <v>886</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>839</v>
+        <v>887</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>840</v>
+        <v>888</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>841</v>
+        <v>889</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>842</v>
+        <v>890</v>
       </c>
     </row>
     <row r="6" ht="156" customHeight="1" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>843</v>
+        <v>891</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>844</v>
+        <v>892</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>845</v>
+        <v>893</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>846</v>
+        <v>894</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>847</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7" ht="198" customHeight="1" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>848</v>
+        <v>896</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>849</v>
+        <v>897</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>850</v>
+        <v>898</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>851</v>
+        <v>899</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>852</v>
+        <v>900</v>
       </c>
     </row>
     <row r="8" ht="211" customHeight="1" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>853</v>
+        <v>901</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>854</v>
+        <v>902</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>855</v>
+        <v>903</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>856</v>
+        <v>904</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>857</v>
+        <v>905</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>858</v>
+        <v>906</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>859</v>
+        <v>907</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>860</v>
+        <v>908</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>861</v>
+        <v>909</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>862</v>
+        <v>910</v>
       </c>
     </row>
     <row r="10" ht="139" customHeight="1" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>863</v>
+        <v>911</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>864</v>
+        <v>912</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>865</v>
+        <v>913</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>866</v>
+        <v>914</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>867</v>
+        <v>915</v>
       </c>
     </row>
     <row r="11" ht="179" customHeight="1" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>868</v>
+        <v>916</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>869</v>
+        <v>917</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>870</v>
+        <v>918</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>871</v>
+        <v>919</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>872</v>
+        <v>920</v>
       </c>
     </row>
     <row r="12" ht="226" customHeight="1" spans="1:6">
       <c r="A12" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>825</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>876</v>
+        <v>924</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>877</v>
+        <v>925</v>
       </c>
     </row>
     <row r="13" ht="120" customHeight="1" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>878</v>
+        <v>926</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>879</v>
+        <v>927</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>880</v>
+        <v>928</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>881</v>
+        <v>929</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>882</v>
+        <v>930</v>
       </c>
     </row>
     <row r="14" ht="120" customHeight="1" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>883</v>
+        <v>931</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>884</v>
+        <v>932</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>885</v>
+        <v>933</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>886</v>
+        <v>934</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>887</v>
+        <v>935</v>
       </c>
     </row>
     <row r="15" ht="120" customHeight="1" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>888</v>
+        <v>936</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>889</v>
+        <v>937</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>890</v>
+        <v>938</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>891</v>
+        <v>939</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>892</v>
+        <v>940</v>
       </c>
     </row>
     <row r="16" ht="120" customHeight="1" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>893</v>
+        <v>941</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>894</v>
+        <v>942</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>895</v>
+        <v>943</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>896</v>
+        <v>944</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>897</v>
+        <v>945</v>
       </c>
     </row>
     <row r="17" ht="120" customHeight="1" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>898</v>
+        <v>946</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>899</v>
+        <v>947</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>900</v>
+        <v>948</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>901</v>
+        <v>949</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>902</v>
+        <v>950</v>
       </c>
     </row>
     <row r="18" ht="120" customHeight="1" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>903</v>
+        <v>951</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>904</v>
+        <v>952</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>905</v>
+        <v>953</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>906</v>
+        <v>954</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>907</v>
+        <v>955</v>
       </c>
     </row>
     <row r="19" ht="120" customHeight="1" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>908</v>
+        <v>956</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>909</v>
+        <v>957</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>910</v>
+        <v>958</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>911</v>
+        <v>959</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>912</v>
+        <v>960</v>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>913</v>
+        <v>961</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>914</v>
+        <v>962</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>915</v>
+        <v>963</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>916</v>
+        <v>964</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>917</v>
+        <v>965</v>
       </c>
     </row>
     <row r="21" ht="198" customHeight="1" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>918</v>
+        <v>966</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>919</v>
+        <v>967</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>920</v>
+        <v>968</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>825</v>
+        <v>873</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>921</v>
+        <v>969</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>922</v>
+        <v>970</v>
       </c>
     </row>
     <row r="22" ht="195" customHeight="1" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>923</v>
+        <v>971</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>924</v>
+        <v>972</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>925</v>
+        <v>973</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>926</v>
+        <v>974</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>927</v>
+        <v>975</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>928</v>
+        <v>976</v>
       </c>
     </row>
     <row r="23" ht="177" customHeight="1" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>929</v>
+        <v>977</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>930</v>
+        <v>978</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>931</v>
+        <v>979</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>932</v>
+        <v>980</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>933</v>
+        <v>981</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>934</v>
+        <v>982</v>
       </c>
     </row>
     <row r="24" ht="165" customHeight="1" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>935</v>
+        <v>983</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>936</v>
+        <v>984</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>937</v>
+        <v>985</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>932</v>
+        <v>980</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>938</v>
+        <v>986</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="25" ht="165" customHeight="1" spans="1:6">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="25" ht="200" customHeight="1" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>940</v>
+        <v>988</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>941</v>
+        <v>989</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>942</v>
+        <v>990</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>932</v>
+        <v>980</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>943</v>
+        <v>991</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>944</v>
+        <v>992</v>
       </c>
     </row>
     <row r="26" ht="162" customHeight="1" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>945</v>
+        <v>993</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>946</v>
+        <v>994</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>947</v>
+        <v>995</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>932</v>
+        <v>980</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>948</v>
+        <v>996</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="27" ht="194" customHeight="1" spans="1:6">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="27" ht="206" customHeight="1" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>950</v>
+        <v>998</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>951</v>
+        <v>999</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>952</v>
+        <v>1000</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>932</v>
+        <v>980</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>953</v>
+        <v>1001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="28" ht="235" customHeight="1" spans="1:6">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="28" ht="248" customHeight="1" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>955</v>
+        <v>1003</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>956</v>
+        <v>1004</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>957</v>
+        <v>1005</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>932</v>
+        <v>980</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>958</v>
+        <v>1006</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>959</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="29" ht="235" customHeight="1" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>960</v>
+        <v>1008</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>961</v>
+        <v>1009</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>962</v>
+        <v>1010</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>932</v>
+        <v>1011</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>963</v>
+        <v>1012</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>964</v>
+        <v>1013</v>
       </c>
     </row>
   </sheetData>
@@ -9255,162 +9585,162 @@
       </c>
     </row>
     <row r="2" ht="227" customHeight="1" spans="1:6">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" ht="169" customHeight="1" spans="1:6">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" ht="218" customHeight="1" spans="1:6">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="16" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" ht="337" customHeight="1" spans="1:6">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" ht="406" customHeight="1" spans="1:6">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="16" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7" ht="215" customHeight="1" spans="1:6">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="16" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" ht="206" customHeight="1" spans="1:6">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="16" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="9" ht="220" customHeight="1" spans="1:6">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>67</v>
       </c>
     </row>
@@ -9423,7 +9753,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -9872,6 +10202,166 @@
       </c>
       <c r="F22" s="14" t="s">
         <v>185</v>
+      </c>
+    </row>
+    <row r="23" ht="192" customHeight="1" spans="1:6">
+      <c r="A23" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" ht="189" spans="1:6">
+      <c r="A24" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" ht="175.5" spans="1:6">
+      <c r="A25" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" ht="189" spans="1:6">
+      <c r="A26" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" ht="202.5" spans="1:6">
+      <c r="A27" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="28" ht="189" spans="1:6">
+      <c r="A28" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="29" ht="175.5" spans="1:6">
+      <c r="A29" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" ht="292" customHeight="1" spans="1:6">
+      <c r="A30" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -9916,302 +10406,302 @@
     </row>
     <row r="2" ht="130" customHeight="1" spans="1:6">
       <c r="A2" s="13" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>190</v>
+        <v>238</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" ht="130" customHeight="1" spans="1:6">
       <c r="A3" s="13" t="s">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>196</v>
+        <v>244</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>197</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1" spans="1:6">
       <c r="A4" s="13" t="s">
-        <v>198</v>
+        <v>246</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" ht="130" customHeight="1" spans="1:6">
       <c r="A5" s="13" t="s">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>205</v>
+        <v>253</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>206</v>
+        <v>254</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>207</v>
+        <v>255</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>208</v>
+        <v>256</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" ht="130" customHeight="1" spans="1:6">
       <c r="A6" s="13" t="s">
-        <v>210</v>
+        <v>258</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>211</v>
+        <v>259</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>212</v>
+        <v>260</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>213</v>
+        <v>261</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>215</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" ht="130" customHeight="1" spans="1:6">
       <c r="A7" s="13" t="s">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>218</v>
+        <v>266</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>213</v>
+        <v>261</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" ht="130" customHeight="1" spans="1:6">
       <c r="A8" s="13" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>225</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" ht="130" customHeight="1" spans="1:6">
       <c r="A9" s="13" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>228</v>
+        <v>276</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>230</v>
+        <v>278</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>231</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" ht="130" customHeight="1" spans="1:6">
       <c r="A10" s="13" t="s">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>235</v>
+        <v>283</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" ht="130" customHeight="1" spans="1:6">
       <c r="A11" s="13" t="s">
-        <v>237</v>
+        <v>285</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>238</v>
+        <v>286</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>239</v>
+        <v>287</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>241</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" ht="130" customHeight="1" spans="1:6">
       <c r="A12" s="13" t="s">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>244</v>
+        <v>292</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>245</v>
+        <v>293</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>246</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" ht="130" customHeight="1" spans="1:6">
       <c r="A13" s="13" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>249</v>
+        <v>297</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>250</v>
+        <v>298</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>251</v>
+        <v>299</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>252</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" ht="130" customHeight="1" spans="1:6">
       <c r="A14" s="13" t="s">
-        <v>253</v>
+        <v>301</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>255</v>
+        <v>303</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>258</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" ht="130" customHeight="1" spans="1:6">
       <c r="A15" s="13" t="s">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>260</v>
+        <v>308</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>261</v>
+        <v>309</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>262</v>
+        <v>310</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>264</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" ht="130" customHeight="1" spans="1:6">
       <c r="A16" s="13" t="s">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>266</v>
+        <v>314</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>267</v>
+        <v>315</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>268</v>
+        <v>316</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>269</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -10256,202 +10746,202 @@
     </row>
     <row r="2" ht="130" customHeight="1" spans="1:6">
       <c r="A2" s="12" t="s">
-        <v>270</v>
+        <v>318</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>275</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" ht="130" customHeight="1" spans="1:6">
       <c r="A3" s="12" t="s">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>278</v>
+        <v>326</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>279</v>
+        <v>327</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>281</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1" spans="1:6">
       <c r="A4" s="12" t="s">
-        <v>282</v>
+        <v>330</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>285</v>
+        <v>333</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>286</v>
+        <v>334</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>287</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" ht="130" customHeight="1" spans="1:6">
       <c r="A5" s="12" t="s">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>289</v>
+        <v>337</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>290</v>
+        <v>338</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>293</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" ht="130" customHeight="1" spans="1:6">
       <c r="A6" s="12" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>295</v>
+        <v>343</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>298</v>
+        <v>346</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>299</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" ht="130" customHeight="1" spans="1:6">
       <c r="A7" s="12" t="s">
-        <v>300</v>
+        <v>348</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>301</v>
+        <v>349</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>303</v>
+        <v>351</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" ht="130" customHeight="1" spans="1:6">
       <c r="A8" s="12" t="s">
-        <v>306</v>
+        <v>354</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>308</v>
+        <v>356</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>309</v>
+        <v>357</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>310</v>
+        <v>358</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>311</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" ht="130" customHeight="1" spans="1:6">
       <c r="A9" s="12" t="s">
-        <v>312</v>
+        <v>360</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>313</v>
+        <v>361</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>315</v>
+        <v>363</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>316</v>
+        <v>364</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" ht="130" customHeight="1" spans="1:6">
       <c r="A10" s="12" t="s">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>285</v>
+        <v>333</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>322</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" ht="130" customHeight="1" spans="1:6">
       <c r="A11" s="12" t="s">
-        <v>323</v>
+        <v>371</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>326</v>
+        <v>374</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -10496,262 +10986,262 @@
     </row>
     <row r="2" ht="353" customHeight="1" spans="1:6">
       <c r="A2" s="11" t="s">
-        <v>329</v>
+        <v>377</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>330</v>
+        <v>378</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>331</v>
+        <v>379</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>333</v>
+        <v>381</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>334</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" ht="130" customHeight="1" spans="1:6">
       <c r="A3" s="11" t="s">
-        <v>335</v>
+        <v>383</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>336</v>
+        <v>384</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>337</v>
+        <v>385</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>338</v>
+        <v>386</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>340</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1" spans="1:6">
       <c r="A4" s="11" t="s">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>343</v>
+        <v>391</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>344</v>
+        <v>392</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>345</v>
+        <v>393</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>346</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" ht="130" customHeight="1" spans="1:6">
       <c r="A5" s="11" t="s">
-        <v>347</v>
+        <v>395</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>351</v>
+        <v>399</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>352</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" ht="130" customHeight="1" spans="1:6">
       <c r="A6" s="11" t="s">
-        <v>353</v>
+        <v>401</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>355</v>
+        <v>403</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>356</v>
+        <v>404</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>357</v>
+        <v>405</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>358</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" ht="130" customHeight="1" spans="1:6">
       <c r="A7" s="11" t="s">
-        <v>359</v>
+        <v>407</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>360</v>
+        <v>408</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>361</v>
+        <v>409</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>362</v>
+        <v>410</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>363</v>
+        <v>411</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>364</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" ht="130" customHeight="1" spans="1:6">
       <c r="A8" s="11" t="s">
-        <v>365</v>
+        <v>413</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>366</v>
+        <v>414</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>367</v>
+        <v>415</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>344</v>
+        <v>392</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>368</v>
+        <v>416</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>369</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" ht="130" customHeight="1" spans="1:6">
       <c r="A9" s="11" t="s">
-        <v>370</v>
+        <v>418</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>371</v>
+        <v>419</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>373</v>
+        <v>421</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>375</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" ht="130" customHeight="1" spans="1:6">
       <c r="A10" s="11" t="s">
-        <v>376</v>
+        <v>424</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>377</v>
+        <v>425</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>380</v>
+        <v>428</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>381</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" ht="130" customHeight="1" spans="1:6">
       <c r="A11" s="11" t="s">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>383</v>
+        <v>431</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>384</v>
+        <v>432</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>385</v>
+        <v>433</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12" ht="130" customHeight="1" spans="1:6">
       <c r="A12" s="11" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>390</v>
+        <v>438</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>391</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" ht="130" customHeight="1" spans="1:6">
       <c r="A13" s="11" t="s">
-        <v>392</v>
+        <v>440</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>393</v>
+        <v>441</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>395</v>
+        <v>443</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>396</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" ht="130" customHeight="1" spans="1:6">
       <c r="A14" s="11" t="s">
-        <v>397</v>
+        <v>445</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>398</v>
+        <v>446</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>399</v>
+        <v>447</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>401</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -10796,242 +11286,242 @@
     </row>
     <row r="2" ht="333" customHeight="1" spans="1:6">
       <c r="A2" s="10" t="s">
-        <v>402</v>
+        <v>450</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>404</v>
+        <v>452</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>405</v>
+        <v>453</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>406</v>
+        <v>454</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>407</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" ht="193" customHeight="1" spans="1:6">
       <c r="A3" s="10" t="s">
-        <v>408</v>
+        <v>456</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>409</v>
+        <v>457</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>410</v>
+        <v>458</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>411</v>
+        <v>459</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1" spans="1:6">
       <c r="A4" s="10" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>415</v>
+        <v>463</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>416</v>
+        <v>464</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>418</v>
+        <v>466</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>419</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5" ht="130" customHeight="1" spans="1:6">
       <c r="A5" s="10" t="s">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>421</v>
+        <v>469</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>422</v>
+        <v>470</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>423</v>
+        <v>471</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>424</v>
+        <v>472</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>425</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" ht="130" customHeight="1" spans="1:6">
       <c r="A6" s="10" t="s">
-        <v>426</v>
+        <v>474</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>427</v>
+        <v>475</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>428</v>
+        <v>476</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>429</v>
+        <v>477</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>430</v>
+        <v>478</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>431</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" ht="130" customHeight="1" spans="1:6">
       <c r="A7" s="10" t="s">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>433</v>
+        <v>481</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>434</v>
+        <v>482</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>435</v>
+        <v>483</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>436</v>
+        <v>484</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>437</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" ht="130" customHeight="1" spans="1:6">
       <c r="A8" s="10" t="s">
-        <v>438</v>
+        <v>486</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>439</v>
+        <v>487</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>441</v>
+        <v>489</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>442</v>
+        <v>490</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>443</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9" ht="130" customHeight="1" spans="1:6">
       <c r="A9" s="10" t="s">
-        <v>444</v>
+        <v>492</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>445</v>
+        <v>493</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>446</v>
+        <v>494</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>441</v>
+        <v>489</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>447</v>
+        <v>495</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>448</v>
+        <v>496</v>
       </c>
     </row>
     <row r="10" ht="130" customHeight="1" spans="1:6">
       <c r="A10" s="10" t="s">
-        <v>449</v>
+        <v>497</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>450</v>
+        <v>498</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>451</v>
+        <v>499</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>441</v>
+        <v>489</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" ht="130" customHeight="1" spans="1:6">
       <c r="A11" s="10" t="s">
-        <v>454</v>
+        <v>502</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>456</v>
+        <v>504</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>441</v>
+        <v>489</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>457</v>
+        <v>505</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>458</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12" ht="130" customHeight="1" spans="1:6">
       <c r="A12" s="10" t="s">
-        <v>459</v>
+        <v>507</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>460</v>
+        <v>508</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>441</v>
+        <v>489</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>462</v>
+        <v>510</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>463</v>
+        <v>511</v>
       </c>
     </row>
     <row r="13" ht="130" customHeight="1" spans="1:6">
       <c r="A13" s="10" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>465</v>
+        <v>513</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>466</v>
+        <v>514</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>467</v>
+        <v>515</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>468</v>
+        <v>516</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>469</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -11076,262 +11566,262 @@
     </row>
     <row r="2" ht="301" customHeight="1" spans="1:6">
       <c r="A2" s="8" t="s">
-        <v>470</v>
+        <v>518</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>471</v>
+        <v>519</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>472</v>
+        <v>520</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>474</v>
+        <v>522</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>475</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" ht="258" customHeight="1" spans="1:6">
       <c r="A3" s="8" t="s">
-        <v>476</v>
+        <v>524</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>477</v>
+        <v>525</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>478</v>
+        <v>526</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>479</v>
+        <v>527</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>480</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4" ht="297" customHeight="1" spans="1:6">
       <c r="A4" s="8" t="s">
-        <v>481</v>
+        <v>529</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>482</v>
+        <v>530</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>483</v>
+        <v>531</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>484</v>
+        <v>532</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>485</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" ht="311" customHeight="1" spans="1:6">
       <c r="A5" s="8" t="s">
-        <v>486</v>
+        <v>534</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>487</v>
+        <v>535</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>488</v>
+        <v>536</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>490</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6" ht="316" customHeight="1" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>491</v>
+        <v>539</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>492</v>
+        <v>540</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>494</v>
+        <v>542</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>495</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" ht="313" customHeight="1" spans="1:6">
       <c r="A7" s="8" t="s">
-        <v>496</v>
+        <v>544</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>497</v>
+        <v>545</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>498</v>
+        <v>546</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>499</v>
+        <v>547</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>500</v>
+        <v>548</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>501</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8" ht="197" customHeight="1" spans="1:6">
       <c r="A8" s="8" t="s">
-        <v>502</v>
+        <v>550</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>503</v>
+        <v>551</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>504</v>
+        <v>552</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>505</v>
+        <v>553</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>506</v>
+        <v>554</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>507</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" ht="312" customHeight="1" spans="1:6">
       <c r="A9" s="8" t="s">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>509</v>
+        <v>557</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>510</v>
+        <v>558</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>511</v>
+        <v>559</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>512</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" ht="247" customHeight="1" spans="1:6">
       <c r="A10" s="8" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>514</v>
+        <v>562</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>515</v>
+        <v>563</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>516</v>
+        <v>564</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>517</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" ht="348" customHeight="1" spans="1:6">
       <c r="A11" s="8" t="s">
-        <v>518</v>
+        <v>566</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>519</v>
+        <v>567</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>520</v>
+        <v>568</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>522</v>
+        <v>570</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>523</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" ht="257" customHeight="1" spans="1:6">
       <c r="A12" s="8" t="s">
-        <v>524</v>
+        <v>572</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>525</v>
+        <v>573</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>526</v>
+        <v>574</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>528</v>
+        <v>576</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>529</v>
+        <v>577</v>
       </c>
     </row>
     <row r="13" ht="343" customHeight="1" spans="1:6">
       <c r="A13" s="8" t="s">
-        <v>530</v>
+        <v>578</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>531</v>
+        <v>579</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>532</v>
+        <v>580</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>533</v>
+        <v>581</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>534</v>
+        <v>582</v>
       </c>
     </row>
     <row r="14" ht="341" customHeight="1" spans="1:6">
       <c r="A14" s="8" t="s">
-        <v>535</v>
+        <v>583</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>536</v>
+        <v>584</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>537</v>
+        <v>585</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>538</v>
+        <v>586</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>539</v>
+        <v>587</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>540</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -11376,202 +11866,202 @@
     </row>
     <row r="2" ht="130" customHeight="1" spans="1:6">
       <c r="A2" s="7" t="s">
-        <v>541</v>
+        <v>589</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>542</v>
+        <v>590</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>543</v>
+        <v>591</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>545</v>
+        <v>593</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>546</v>
+        <v>594</v>
       </c>
     </row>
     <row r="3" ht="130" customHeight="1" spans="1:6">
       <c r="A3" s="7" t="s">
-        <v>547</v>
+        <v>595</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>548</v>
+        <v>596</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>549</v>
+        <v>597</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>550</v>
+        <v>598</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>551</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1" spans="1:6">
       <c r="A4" s="7" t="s">
-        <v>552</v>
+        <v>600</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>553</v>
+        <v>601</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>554</v>
+        <v>602</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>555</v>
+        <v>603</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>556</v>
+        <v>604</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>557</v>
+        <v>605</v>
       </c>
     </row>
     <row r="5" ht="130" customHeight="1" spans="1:6">
       <c r="A5" s="7" t="s">
-        <v>558</v>
+        <v>606</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>559</v>
+        <v>607</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>560</v>
+        <v>608</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>561</v>
+        <v>609</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>562</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" ht="130" customHeight="1" spans="1:6">
       <c r="A6" s="7" t="s">
-        <v>563</v>
+        <v>611</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>564</v>
+        <v>612</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>565</v>
+        <v>613</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>566</v>
+        <v>614</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>567</v>
+        <v>615</v>
       </c>
     </row>
     <row r="7" ht="130" customHeight="1" spans="1:6">
       <c r="A7" s="7" t="s">
-        <v>568</v>
+        <v>616</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>570</v>
+        <v>618</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>571</v>
+        <v>619</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>572</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8" ht="130" customHeight="1" spans="1:6">
       <c r="A8" s="7" t="s">
-        <v>573</v>
+        <v>621</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>574</v>
+        <v>622</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>575</v>
+        <v>623</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>576</v>
+        <v>624</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>577</v>
+        <v>625</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>578</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9" ht="130" customHeight="1" spans="1:6">
       <c r="A9" s="7" t="s">
-        <v>579</v>
+        <v>627</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>580</v>
+        <v>628</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>581</v>
+        <v>629</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>582</v>
+        <v>630</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>583</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" ht="130" customHeight="1" spans="1:6">
       <c r="A10" s="7" t="s">
-        <v>584</v>
+        <v>632</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>585</v>
+        <v>633</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>586</v>
+        <v>634</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>587</v>
+        <v>635</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>588</v>
+        <v>636</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>589</v>
+        <v>637</v>
       </c>
     </row>
     <row r="11" ht="130" customHeight="1" spans="1:6">
       <c r="A11" s="7" t="s">
-        <v>590</v>
+        <v>638</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>591</v>
+        <v>639</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>544</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>593</v>
+        <v>641</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>594</v>
+        <v>642</v>
       </c>
     </row>
   </sheetData>

--- a/docker-authz-proxy-testcases-v6.xlsx
+++ b/docker-authz-proxy-testcases-v6.xlsx
@@ -1531,7 +1531,7 @@
   </si>
   <si>
     <t>1. 确认初始状态（alice 无法拉取）：
-   sudo -u alice docker -H unix:///var/run/docker-authz.sock pull busybox:latest
+   sudo -u alice docker -H unix:///run/docker-authz/alice/sock.sock pull busybox:latest
    # 预期失败
 2. root 将 busybox:latest 设为 public：
    docker-authz-proxy-ctl image set-public busybox:latest

--- a/docker-authz-proxy-testcases-v6.xlsx
+++ b/docker-authz-proxy-testcases-v6.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="24000" windowHeight="11055" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例汇总" sheetId="1" r:id="rId1"/>
@@ -10397,7 +10397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="130" customHeight="1" spans="1:6">
+    <row r="2" ht="381" customHeight="1" spans="1:6">
       <c r="A2" s="13" t="s">
         <v>234</v>
       </c>
